--- a/worklog/v2.2.3/s10/pjm/v3/test/ods_tech_state_v2.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v3/test/ods_tech_state_v2.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t>项目编号</t>
   </si>
@@ -490,124 +490,145 @@
     <t>PJ-2025-007</t>
   </si>
   <si>
-    <t>2025.3.15</t>
+    <t>2025年3月25日</t>
   </si>
   <si>
     <t>PJ-2025-008</t>
   </si>
   <si>
-    <t>待定</t>
-  </si>
-  <si>
-    <t>20205/05/15</t>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>PJ-2025-006</t>
+  </si>
+  <si>
+    <t>20205/04/01</t>
+  </si>
+  <si>
+    <t>2025/04/03</t>
+  </si>
+  <si>
+    <t>2025-03-32</t>
+  </si>
+  <si>
+    <t>PJ-2025-004</t>
+  </si>
+  <si>
+    <t>2025-04-32</t>
+  </si>
+  <si>
+    <t>PJ-2025-003</t>
+  </si>
+  <si>
+    <t>2025/06/30</t>
+  </si>
+  <si>
+    <t>2025/3/25</t>
+  </si>
+  <si>
+    <t>2025/4/5</t>
+  </si>
+  <si>
+    <t>2025/04/01</t>
+  </si>
+  <si>
+    <t>2025-03</t>
+  </si>
+  <si>
+    <t>PJ-2025-005</t>
+  </si>
+  <si>
+    <t>2025/7/31</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>20205/03/20</t>
+  </si>
+  <si>
+    <t>20250/03/20</t>
   </si>
   <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>2025-02-30</t>
-  </si>
-  <si>
-    <t>2025-4-5</t>
+    <t>2025年4月30日</t>
+  </si>
+  <si>
+    <t>20205/06/30</t>
+  </si>
+  <si>
+    <t>20205/03/15</t>
+  </si>
+  <si>
+    <t>20250/05/01</t>
+  </si>
+  <si>
+    <t>2025年07月31日</t>
+  </si>
+  <si>
+    <t>2025-13-15</t>
+  </si>
+  <si>
+    <t>2025-13-20</t>
   </si>
   <si>
     <t>20250/04/10</t>
   </si>
   <si>
-    <t>PJ-2025-006</t>
+    <t>2025/03/20</t>
+  </si>
+  <si>
+    <t>2025/3/15</t>
+  </si>
+  <si>
+    <t>20205/04/05</t>
+  </si>
+  <si>
+    <t>2025/3/20</t>
+  </si>
+  <si>
+    <t>2025-3-15</t>
+  </si>
+  <si>
+    <t>2025/04/10</t>
+  </si>
+  <si>
+    <t>2025/5/15</t>
+  </si>
+  <si>
+    <t>2025.1.20</t>
+  </si>
+  <si>
+    <t>20205/02/28</t>
+  </si>
+  <si>
+    <t>2025/2/5</t>
+  </si>
+  <si>
+    <t>2025年03月24日</t>
   </si>
   <si>
     <t>2025-13-25</t>
   </si>
   <si>
-    <t>2025-04-32</t>
-  </si>
-  <si>
-    <t>PJ-2025-005</t>
-  </si>
-  <si>
-    <t>2025年6月30日</t>
-  </si>
-  <si>
-    <t>2025/04/01</t>
-  </si>
-  <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>2025年1月20日</t>
-  </si>
-  <si>
-    <t>2025年3月15日</t>
-  </si>
-  <si>
-    <t>2025-13-31</t>
-  </si>
-  <si>
-    <t>2025-4-1</t>
-  </si>
-  <si>
-    <t>2025/03/28</t>
-  </si>
-  <si>
-    <t>PJ-2025-003</t>
-  </si>
-  <si>
-    <t>2025-03</t>
-  </si>
-  <si>
-    <t>20250/02/05</t>
-  </si>
-  <si>
-    <t>2025/03/15</t>
-  </si>
-  <si>
-    <t>2025/4/30</t>
+    <t>20205/03/12</t>
+  </si>
+  <si>
+    <t>2025.2.5</t>
+  </si>
+  <si>
+    <t>2025-04</t>
   </si>
   <si>
     <t>2025/05/15</t>
   </si>
   <si>
-    <t>PJ-2025-004</t>
-  </si>
-  <si>
-    <t>20250/02/28</t>
-  </si>
-  <si>
-    <t>2025.4.10</t>
-  </si>
-  <si>
-    <t>2025年07月31日</t>
-  </si>
-  <si>
-    <t>2025/04/10</t>
-  </si>
-  <si>
-    <t>2025-13-01</t>
-  </si>
-  <si>
-    <t>2025-3-18</t>
-  </si>
-  <si>
     <t>2025年4月10日</t>
   </si>
   <si>
-    <t>2025-3-24</t>
-  </si>
-  <si>
-    <t>2025.3.25</t>
-  </si>
-  <si>
-    <t>2025-03-32</t>
-  </si>
-  <si>
-    <t>2025-04</t>
-  </si>
-  <si>
-    <t>2025年3月5日</t>
-  </si>
-  <si>
-    <t>2025年4月5日</t>
+    <t>2025/02/25</t>
   </si>
 </sst>
 </file>
@@ -1526,7 +1547,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -1645,7 +1666,7 @@
         <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
         <v>47</v>
@@ -1728,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
@@ -1829,7 +1850,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
         <v>102</v>
@@ -1847,7 +1868,7 @@
         <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="H13" t="s">
         <v>105</v>
@@ -1868,7 +1889,7 @@
         <v>91</v>
       </c>
       <c r="N13" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
         <v>108</v>
@@ -1916,7 +1937,7 @@
         <v>79</v>
       </c>
       <c r="AD13" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="AE13" t="s">
         <v>95</v>
@@ -1930,7 +1951,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>116</v>
@@ -1975,7 +1996,7 @@
         <v>93</v>
       </c>
       <c r="P14" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q14" t="s">
         <v>125</v>
@@ -2031,7 +2052,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s">
         <v>131</v>
@@ -2049,7 +2070,7 @@
         <v>135</v>
       </c>
       <c r="G15" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="H15" t="s">
         <v>105</v>
@@ -2118,7 +2139,7 @@
         <v>58</v>
       </c>
       <c r="AD15" t="s">
-        <v>59</v>
+        <v>162</v>
       </c>
       <c r="AE15" t="s">
         <v>60</v>
@@ -2132,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B16" t="s">
         <v>141</v>
@@ -2150,7 +2171,7 @@
         <v>120</v>
       </c>
       <c r="G16" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
         <v>93</v>
@@ -2159,7 +2180,7 @@
         <v>41</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="K16" t="s">
         <v>105</v>
@@ -2177,7 +2198,7 @@
         <v>105</v>
       </c>
       <c r="P16" t="s">
-        <v>167</v>
+        <v>59</v>
       </c>
       <c r="Q16" t="s">
         <v>60</v>
@@ -2201,7 +2222,7 @@
         <v>54</v>
       </c>
       <c r="X16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y16" t="s">
         <v>105</v>
@@ -2233,7 +2254,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s">
         <v>149</v>
@@ -2251,7 +2272,7 @@
         <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="H17" t="s">
         <v>43</v>
@@ -2272,7 +2293,7 @@
         <v>91</v>
       </c>
       <c r="N17" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="O17" t="s">
         <v>105</v>
@@ -2334,7 +2355,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -2435,7 +2456,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>63</v>
@@ -2453,7 +2474,7 @@
         <v>67</v>
       </c>
       <c r="G19" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="H19" t="s">
         <v>47</v>
@@ -2522,7 +2543,7 @@
         <v>79</v>
       </c>
       <c r="AD19" t="s">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="AE19" t="s">
         <v>60</v>
@@ -2536,7 +2557,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s">
         <v>81</v>
@@ -2614,7 +2635,7 @@
         <v>100</v>
       </c>
       <c r="AA20" t="s">
-        <v>59</v>
+        <v>168</v>
       </c>
       <c r="AB20" t="s">
         <v>60</v>
@@ -2637,7 +2658,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B21" t="s">
         <v>102</v>
@@ -2655,7 +2676,7 @@
         <v>38</v>
       </c>
       <c r="G21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H21" t="s">
         <v>105</v>
@@ -2682,7 +2703,7 @@
         <v>108</v>
       </c>
       <c r="P21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q21" t="s">
         <v>110</v>
@@ -2724,7 +2745,7 @@
         <v>79</v>
       </c>
       <c r="AD21" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="AE21" t="s">
         <v>95</v>
@@ -2738,7 +2759,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s">
         <v>116</v>
@@ -2783,7 +2804,7 @@
         <v>93</v>
       </c>
       <c r="P22" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="Q22" t="s">
         <v>125</v>
@@ -2825,7 +2846,7 @@
         <v>58</v>
       </c>
       <c r="AD22" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="AE22" t="s">
         <v>125</v>
@@ -2839,7 +2860,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
         <v>131</v>
@@ -2857,7 +2878,7 @@
         <v>135</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="H23" t="s">
         <v>105</v>
@@ -2940,7 +2961,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s">
         <v>141</v>
@@ -2967,7 +2988,7 @@
         <v>41</v>
       </c>
       <c r="J24" t="s">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="K24" t="s">
         <v>105</v>
@@ -3041,7 +3062,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B25" t="s">
         <v>149</v>
@@ -3068,7 +3089,7 @@
         <v>41</v>
       </c>
       <c r="J25" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s">
         <v>93</v>
@@ -3080,7 +3101,7 @@
         <v>91</v>
       </c>
       <c r="N25" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="O25" t="s">
         <v>105</v>
@@ -3110,7 +3131,7 @@
         <v>54</v>
       </c>
       <c r="X25" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="Y25" t="s">
         <v>125</v>
@@ -3128,7 +3149,7 @@
         <v>79</v>
       </c>
       <c r="AD25" t="s">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="AE25" t="s">
         <v>60</v>
@@ -3142,7 +3163,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -3160,7 +3181,7 @@
         <v>38</v>
       </c>
       <c r="G26" t="s">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="H26" t="s">
         <v>40</v>
@@ -3243,7 +3264,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
         <v>63</v>
@@ -3261,7 +3282,7 @@
         <v>67</v>
       </c>
       <c r="G27" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="H27" t="s">
         <v>47</v>
@@ -3288,7 +3309,7 @@
         <v>49</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q27" t="s">
         <v>72</v>
@@ -3344,7 +3365,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
         <v>81</v>
@@ -3389,7 +3410,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="Q28" t="s">
         <v>95</v>
@@ -3445,7 +3466,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="B29" t="s">
         <v>102</v>
@@ -3463,7 +3484,7 @@
         <v>38</v>
       </c>
       <c r="G29" t="s">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="H29" t="s">
         <v>105</v>
@@ -3546,7 +3567,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
         <v>116</v>
@@ -3647,7 +3668,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>131</v>
@@ -3734,7 +3755,7 @@
         <v>58</v>
       </c>
       <c r="AD31" t="s">
-        <v>59</v>
+        <v>168</v>
       </c>
       <c r="AE31" t="s">
         <v>60</v>
@@ -3748,7 +3769,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="B32" t="s">
         <v>141</v>
@@ -3766,7 +3787,7 @@
         <v>120</v>
       </c>
       <c r="G32" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="H32" t="s">
         <v>93</v>
@@ -3775,7 +3796,7 @@
         <v>41</v>
       </c>
       <c r="J32" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="K32" t="s">
         <v>105</v>
@@ -3849,7 +3870,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
         <v>149</v>
@@ -3876,7 +3897,7 @@
         <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="K33" t="s">
         <v>93</v>
@@ -3888,7 +3909,7 @@
         <v>91</v>
       </c>
       <c r="N33" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="O33" t="s">
         <v>105</v>
@@ -3918,7 +3939,7 @@
         <v>54</v>
       </c>
       <c r="X33" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="Y33" t="s">
         <v>125</v>
@@ -3950,7 +3971,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
@@ -3977,7 +3998,7 @@
         <v>41</v>
       </c>
       <c r="J34" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="K34" t="s">
         <v>43</v>
@@ -3989,13 +4010,13 @@
         <v>45</v>
       </c>
       <c r="N34" t="s">
-        <v>181</v>
+        <v>46</v>
       </c>
       <c r="O34" t="s">
         <v>47</v>
       </c>
       <c r="P34" t="s">
-        <v>48</v>
+        <v>181</v>
       </c>
       <c r="Q34" t="s">
         <v>49</v>
@@ -4152,7 +4173,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>81</v>
@@ -4170,7 +4191,7 @@
         <v>85</v>
       </c>
       <c r="G36" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s">
         <v>87</v>
@@ -4221,7 +4242,7 @@
         <v>54</v>
       </c>
       <c r="X36" t="s">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="Y36" t="s">
         <v>93</v>
@@ -4230,7 +4251,7 @@
         <v>100</v>
       </c>
       <c r="AA36" t="s">
-        <v>59</v>
+        <v>177</v>
       </c>
       <c r="AB36" t="s">
         <v>60</v>
@@ -4253,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
         <v>102</v>
@@ -4292,13 +4313,13 @@
         <v>91</v>
       </c>
       <c r="N37" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="O37" t="s">
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="Q37" t="s">
         <v>110</v>
@@ -4354,7 +4375,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="B38" t="s">
         <v>116</v>
@@ -4381,7 +4402,7 @@
         <v>41</v>
       </c>
       <c r="J38" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="K38" t="s">
         <v>47</v>
@@ -4393,7 +4414,7 @@
         <v>123</v>
       </c>
       <c r="N38" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="O38" t="s">
         <v>93</v>
@@ -4556,7 +4577,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="B40" t="s">
         <v>141</v>
@@ -4574,7 +4595,7 @@
         <v>120</v>
       </c>
       <c r="G40" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="H40" t="s">
         <v>93</v>
@@ -4595,7 +4616,7 @@
         <v>123</v>
       </c>
       <c r="N40" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="O40" t="s">
         <v>105</v>
@@ -4625,7 +4646,7 @@
         <v>54</v>
       </c>
       <c r="X40" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="Y40" t="s">
         <v>105</v>
@@ -4657,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B41" t="s">
         <v>149</v>
@@ -4758,7 +4779,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -4797,13 +4818,13 @@
         <v>45</v>
       </c>
       <c r="N42" t="s">
-        <v>46</v>
+        <v>183</v>
       </c>
       <c r="O42" t="s">
         <v>47</v>
       </c>
       <c r="P42" t="s">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="Q42" t="s">
         <v>49</v>
@@ -4859,7 +4880,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="B43" t="s">
         <v>63</v>
@@ -4898,13 +4919,13 @@
         <v>45</v>
       </c>
       <c r="N43" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="O43" t="s">
         <v>49</v>
       </c>
       <c r="P43" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="Q43" t="s">
         <v>72</v>
@@ -4946,7 +4967,7 @@
         <v>79</v>
       </c>
       <c r="AD43" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="AE43" t="s">
         <v>60</v>
@@ -4960,7 +4981,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
         <v>81</v>
@@ -5061,7 +5082,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
         <v>102</v>
@@ -5100,7 +5121,7 @@
         <v>91</v>
       </c>
       <c r="N45" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O45" t="s">
         <v>108</v>
@@ -5162,7 +5183,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
         <v>116</v>
@@ -5201,7 +5222,7 @@
         <v>123</v>
       </c>
       <c r="N46" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="O46" t="s">
         <v>93</v>
@@ -5263,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="B47" t="s">
         <v>131</v>
@@ -5364,7 +5385,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
         <v>141</v>
@@ -5382,7 +5403,7 @@
         <v>120</v>
       </c>
       <c r="G48" t="s">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="H48" t="s">
         <v>93</v>
@@ -5465,7 +5486,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
         <v>149</v>
@@ -5492,7 +5513,7 @@
         <v>41</v>
       </c>
       <c r="J49" t="s">
-        <v>162</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s">
         <v>93</v>
@@ -5566,7 +5587,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="B50" t="s">
         <v>34</v>
@@ -5593,7 +5614,7 @@
         <v>41</v>
       </c>
       <c r="J50" t="s">
-        <v>187</v>
+        <v>42</v>
       </c>
       <c r="K50" t="s">
         <v>43</v>
@@ -5653,7 +5674,7 @@
         <v>58</v>
       </c>
       <c r="AD50" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="AE50" t="s">
         <v>60</v>
@@ -5667,7 +5688,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B51" t="s">
         <v>63</v>
@@ -5768,7 +5789,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>159</v>
+        <v>62</v>
       </c>
       <c r="B52" t="s">
         <v>81</v>
@@ -5807,7 +5828,7 @@
         <v>91</v>
       </c>
       <c r="N52" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="O52" t="s">
         <v>93</v>
@@ -5837,7 +5858,7 @@
         <v>54</v>
       </c>
       <c r="X52" t="s">
-        <v>99</v>
+        <v>177</v>
       </c>
       <c r="Y52" t="s">
         <v>93</v>
@@ -5855,7 +5876,7 @@
         <v>58</v>
       </c>
       <c r="AD52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AE52" t="s">
         <v>60</v>
@@ -5869,7 +5890,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="B53" t="s">
         <v>102</v>
@@ -5970,7 +5991,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B54" t="s">
         <v>116</v>
@@ -5997,7 +6018,7 @@
         <v>41</v>
       </c>
       <c r="J54" t="s">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="K54" t="s">
         <v>47</v>
@@ -6015,7 +6036,7 @@
         <v>93</v>
       </c>
       <c r="P54" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="Q54" t="s">
         <v>125</v>
@@ -6071,7 +6092,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B55" t="s">
         <v>131</v>
@@ -6089,7 +6110,7 @@
         <v>135</v>
       </c>
       <c r="G55" t="s">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="H55" t="s">
         <v>105</v>
@@ -6158,7 +6179,7 @@
         <v>58</v>
       </c>
       <c r="AD55" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="AE55" t="s">
         <v>60</v>
@@ -6172,7 +6193,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="B56" t="s">
         <v>141</v>
@@ -6217,7 +6238,7 @@
         <v>105</v>
       </c>
       <c r="P56" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="Q56" t="s">
         <v>60</v>
@@ -6241,7 +6262,7 @@
         <v>54</v>
       </c>
       <c r="X56" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="Y56" t="s">
         <v>105</v>
@@ -6300,7 +6321,7 @@
         <v>41</v>
       </c>
       <c r="J57" t="s">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="K57" t="s">
         <v>93</v>
@@ -6374,7 +6395,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B58" t="s">
         <v>34</v>
@@ -6475,7 +6496,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B59" t="s">
         <v>63</v>
@@ -6520,7 +6541,7 @@
         <v>49</v>
       </c>
       <c r="P59" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="Q59" t="s">
         <v>72</v>
@@ -6562,7 +6583,7 @@
         <v>79</v>
       </c>
       <c r="AD59" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="AE59" t="s">
         <v>60</v>
@@ -6576,7 +6597,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B60" t="s">
         <v>81</v>
@@ -6615,7 +6636,7 @@
         <v>91</v>
       </c>
       <c r="N60" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="O60" t="s">
         <v>93</v>
@@ -6654,7 +6675,7 @@
         <v>100</v>
       </c>
       <c r="AA60" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="AB60" t="s">
         <v>60</v>
@@ -6677,7 +6698,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B61" t="s">
         <v>102</v>
@@ -6778,7 +6799,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>186</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
         <v>116</v>
@@ -6805,7 +6826,7 @@
         <v>41</v>
       </c>
       <c r="J62" t="s">
-        <v>46</v>
+        <v>193</v>
       </c>
       <c r="K62" t="s">
         <v>47</v>
@@ -6817,7 +6838,7 @@
         <v>123</v>
       </c>
       <c r="N62" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="O62" t="s">
         <v>93</v>
@@ -6879,7 +6900,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="B63" t="s">
         <v>131</v>
@@ -6966,7 +6987,7 @@
         <v>58</v>
       </c>
       <c r="AD63" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="AE63" t="s">
         <v>60</v>
@@ -6980,7 +7001,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="B64" t="s">
         <v>141</v>
@@ -7007,7 +7028,7 @@
         <v>41</v>
       </c>
       <c r="J64" t="s">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="K64" t="s">
         <v>105</v>
@@ -7081,7 +7102,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B65" t="s">
         <v>149</v>
@@ -7108,7 +7129,7 @@
         <v>41</v>
       </c>
       <c r="J65" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="K65" t="s">
         <v>93</v>
@@ -7120,13 +7141,13 @@
         <v>91</v>
       </c>
       <c r="N65" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="O65" t="s">
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>107</v>
+        <v>195</v>
       </c>
       <c r="Q65" t="s">
         <v>108</v>
@@ -7182,7 +7203,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B66" t="s">
         <v>34</v>
@@ -7200,7 +7221,7 @@
         <v>38</v>
       </c>
       <c r="G66" t="s">
-        <v>39</v>
+        <v>196</v>
       </c>
       <c r="H66" t="s">
         <v>40</v>
@@ -7209,7 +7230,7 @@
         <v>41</v>
       </c>
       <c r="J66" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="K66" t="s">
         <v>43</v>
@@ -7221,7 +7242,7 @@
         <v>45</v>
       </c>
       <c r="N66" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="O66" t="s">
         <v>47</v>
@@ -7283,7 +7304,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="B67" t="s">
         <v>63</v>
@@ -7384,7 +7405,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B68" t="s">
         <v>81</v>
@@ -7402,7 +7423,7 @@
         <v>85</v>
       </c>
       <c r="G68" t="s">
-        <v>86</v>
+        <v>198</v>
       </c>
       <c r="H68" t="s">
         <v>87</v>
@@ -7423,7 +7444,7 @@
         <v>91</v>
       </c>
       <c r="N68" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="O68" t="s">
         <v>93</v>
@@ -7453,7 +7474,7 @@
         <v>54</v>
       </c>
       <c r="X68" t="s">
-        <v>192</v>
+        <v>99</v>
       </c>
       <c r="Y68" t="s">
         <v>93</v>
@@ -7462,7 +7483,7 @@
         <v>100</v>
       </c>
       <c r="AA68" t="s">
-        <v>193</v>
+        <v>59</v>
       </c>
       <c r="AB68" t="s">
         <v>60</v>
@@ -7485,7 +7506,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B69" t="s">
         <v>102</v>
@@ -7572,7 +7593,7 @@
         <v>79</v>
       </c>
       <c r="AD69" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="AE69" t="s">
         <v>95</v>
@@ -7586,7 +7607,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
         <v>116</v>
@@ -7664,7 +7685,7 @@
         <v>100</v>
       </c>
       <c r="AA70" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AB70" t="s">
         <v>125</v>
@@ -7673,7 +7694,7 @@
         <v>58</v>
       </c>
       <c r="AD70" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AE70" t="s">
         <v>125</v>
@@ -7687,7 +7708,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
         <v>131</v>
@@ -7788,7 +7809,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
         <v>141</v>
@@ -7866,7 +7887,7 @@
         <v>100</v>
       </c>
       <c r="AA72" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AB72" t="s">
         <v>60</v>
@@ -7875,7 +7896,7 @@
         <v>79</v>
       </c>
       <c r="AD72" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="AE72" t="s">
         <v>60</v>
@@ -7889,7 +7910,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="B73" t="s">
         <v>149</v>
@@ -7907,7 +7928,7 @@
         <v>85</v>
       </c>
       <c r="G73" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="H73" t="s">
         <v>43</v>
@@ -7916,7 +7937,7 @@
         <v>41</v>
       </c>
       <c r="J73" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="K73" t="s">
         <v>93</v>
@@ -7934,7 +7955,7 @@
         <v>105</v>
       </c>
       <c r="P73" t="s">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="Q73" t="s">
         <v>108</v>
@@ -7976,7 +7997,7 @@
         <v>79</v>
       </c>
       <c r="AD73" t="s">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="AE73" t="s">
         <v>60</v>
@@ -7990,7 +8011,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="B74" t="s">
         <v>34</v>
@@ -8029,7 +8050,7 @@
         <v>45</v>
       </c>
       <c r="N74" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="O74" t="s">
         <v>47</v>
@@ -8059,7 +8080,7 @@
         <v>54</v>
       </c>
       <c r="X74" t="s">
-        <v>55</v>
+        <v>201</v>
       </c>
       <c r="Y74" t="s">
         <v>47</v>
@@ -8091,7 +8112,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="B75" t="s">
         <v>63</v>
@@ -8192,7 +8213,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="B76" t="s">
         <v>81</v>
@@ -8210,7 +8231,7 @@
         <v>85</v>
       </c>
       <c r="G76" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="H76" t="s">
         <v>87</v>
@@ -8219,7 +8240,7 @@
         <v>41</v>
       </c>
       <c r="J76" t="s">
-        <v>198</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s">
         <v>89</v>
@@ -8231,7 +8252,7 @@
         <v>91</v>
       </c>
       <c r="N76" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="O76" t="s">
         <v>93</v>
@@ -8293,7 +8314,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
         <v>102</v>
@@ -8311,7 +8332,7 @@
         <v>38</v>
       </c>
       <c r="G77" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H77" t="s">
         <v>105</v>
@@ -8332,7 +8353,7 @@
         <v>91</v>
       </c>
       <c r="N77" t="s">
-        <v>107</v>
+        <v>204</v>
       </c>
       <c r="O77" t="s">
         <v>108</v>
@@ -8394,7 +8415,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B78" t="s">
         <v>116</v>
@@ -8463,7 +8484,7 @@
         <v>54</v>
       </c>
       <c r="X78" t="s">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="Y78" t="s">
         <v>93</v>
@@ -8495,7 +8516,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="B79" t="s">
         <v>131</v>
@@ -8513,7 +8534,7 @@
         <v>135</v>
       </c>
       <c r="G79" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="H79" t="s">
         <v>105</v>
@@ -8596,7 +8617,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B80" t="s">
         <v>141</v>
@@ -8614,7 +8635,7 @@
         <v>120</v>
       </c>
       <c r="G80" t="s">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="H80" t="s">
         <v>93</v>
@@ -8683,7 +8704,7 @@
         <v>79</v>
       </c>
       <c r="AD80" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="AE80" t="s">
         <v>60</v>
@@ -8697,7 +8718,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
         <v>149</v>
@@ -8715,7 +8736,7 @@
         <v>85</v>
       </c>
       <c r="G81" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="H81" t="s">
         <v>43</v>
